--- a/docs/package/05_Delivery/Upload_Templates/Company_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Company_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="90">
   <si>
     <t xml:space="preserve">Company Code</t>
   </si>
@@ -51,133 +51,139 @@
     <t xml:space="preserve">Address Line 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Pin Code</t>
+    <t xml:space="preserve">ZIP Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">City / Municipality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Province</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phone Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Letterhead company - used on documents and reports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bayanihan Insurance Brokers Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC-BR-2026-0142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">008-765-432-000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">info@bayanihanbrokers.example.ph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://bayanihanbrokers.example.ph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-life insurance broker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/F Ayala Tower One</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ayala Avenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Makati City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metro Manila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Philippines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+63 2 8812 4400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allowed values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other accepted headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CompanyCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CompanyName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LicenseNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDOCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-mail address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EmailID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Web address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Websitelink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AddressLine1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AddressLine2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AddressLine3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PinCode</t>
   </si>
   <si>
     <t xml:space="preserve">City</t>
   </si>
   <si>
     <t xml:space="preserve">State</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Country</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phone Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Letterhead company - used on documents and reports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BIB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bayanihan Insurance Brokers Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IC-BR-2026-0142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">008-765-432-000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@bayanihanbrokers.example.ph</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://bayanihanbrokers.example.ph</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-life insurance broker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18/F Ayala Tower One</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ayala Avenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Makati</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metro Manila</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Philippines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+63 2 8812 4400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Format</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allowed values</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Example</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other accepted headers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CompanyCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CompanyName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LicenseNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RDOCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-mail address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EmailID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Web address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Websitelink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddressLine1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddressLine2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddressLine3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PinCode</t>
   </si>
   <si>
     <t xml:space="preserve">PhoneNumber</t>
@@ -421,7 +427,7 @@
     <col min="11" max="11" width="20" customWidth="1"/>
     <col min="12" max="12" width="20" customWidth="1"/>
     <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="14" max="14" width="25" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
     <col min="17" max="17" width="18" customWidth="1"/>
@@ -793,6 +799,9 @@
       <c r="E15" s="0" t="s">
         <v>30</v>
       </c>
+      <c r="F15" s="4" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
@@ -807,6 +816,9 @@
       <c r="E16" s="0" t="s">
         <v>31</v>
       </c>
+      <c r="F16" s="4" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
@@ -836,7 +848,7 @@
         <v>33</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -858,13 +870,13 @@
         <v>34</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E20" s="0" t="s">
         <v>34</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21">
@@ -875,13 +887,13 @@
         <v>34</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -900,111 +912,111 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/docs/package/05_Delivery/Upload_Templates/Company_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Company_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="88">
   <si>
     <t xml:space="preserve">Company Code</t>
   </si>
@@ -222,12 +222,6 @@
     <t xml:space="preserve">Master &gt; Generals &gt; Organization &gt; Company (no Upload button on this screen yet: a System Administrator uploads the file through the API route)</t>
   </si>
   <si>
-    <t xml:space="preserve">API route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /api/masters/company/upload (multipart field "file")</t>
-  </si>
-  <si>
     <t xml:space="preserve">File types</t>
   </si>
   <si>
@@ -258,10 +252,10 @@
     <t xml:space="preserve">The rows under the header on the Data sheet are samples. Delete them before you upload your own data.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dates and amounts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter dates as YYYY-MM-DD and amounts as plain numbers (no peso sign, no thousands separator). The Data sheet cells are formatted as text so that Excel keeps what you type.</t>
+    <t xml:space="preserve">Amounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter amounts as plain numbers (no peso sign, no thousands separator). The Data sheet cells are formatted as text so that Excel keeps what you type.</t>
   </si>
   <si>
     <t xml:space="preserve">What happens on errors</t>
@@ -279,10 +273,10 @@
     <t xml:space="preserve">The primary company (Is Primary = Yes) is the letterhead of every document and report; only one active company may be primary. Replace the shipped iorta TechNXT record with your own company by editing it on the screen.</t>
   </si>
   <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated by backend/scripts/build-upload-templates.js from the column list the importer itself uses. Do not rename the headers.</t>
+    <t xml:space="preserve">Headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The headers are the ones the import reads. Do not rename them.</t>
   </si>
 </sst>
 </file>
@@ -290,9 +284,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -319,8 +313,42 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0B2A4A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF5F6B76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -348,6 +376,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF4CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -379,9 +425,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -402,6 +448,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -903,7 +956,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -999,24 +1052,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="s">
+      <c r="B12" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B12" s="4" t="s">
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="13">
       <c r="B13" s="4" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>
